--- a/backtest_runs/20260410_193731/by_symbol/FPJM/FPJM.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/FPJM/FPJM.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>112000.24</v>
@@ -817,7 +817,7 @@
         <v>-4333.420000000011</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>113333.6</v>
@@ -909,7 +909,7 @@
         <v>-4666.760000000004</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>110500.21</v>
@@ -955,7 +955,7 @@
         <v>-2666.720000000003</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>107833.49</v>
@@ -1185,7 +1185,7 @@
         <v>-666.6799999999857</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>107500.15</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>107500.15</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>107500.15</v>
@@ -1415,7 +1415,7 @@
         <v>-1500.029999999998</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>111333.56</v>
@@ -1461,7 +1461,7 @@
         <v>-5000.100000000012</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>106333.46</v>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>108666.84</v>
@@ -1645,7 +1645,7 @@
         <v>-3500.069999999999</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>105166.77</v>
